--- a/data/sports/tennis/research.xlsx
+++ b/data/sports/tennis/research.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$DP$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$DQ$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -32,6 +34,11 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -67,11 +74,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -137,65 +139,65 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -883,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DP1"/>
+  <dimension ref="A1:DQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1006,6 +1008,7 @@
     <col width="20" customWidth="1" min="118" max="118"/>
     <col width="20" customWidth="1" min="119" max="119"/>
     <col width="22" customWidth="1" min="120" max="120"/>
+    <col width="22" customWidth="1" min="121" max="121"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1609,9 +1612,14 @@
           <t>serving_policy_block_reason</t>
         </is>
       </c>
+      <c r="DQ1" s="23" t="inlineStr">
+        <is>
+          <t>model_input_snapshot_json</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:DP1"/>
+  <autoFilter ref="A1:DQ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
